--- a/artfynd/A 20065-2026 artfynd.xlsx
+++ b/artfynd/A 20065-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,14 +675,14 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>133114986</v>
+        <v>133114985</v>
       </c>
       <c r="B2" t="n">
-        <v>79334</v>
+        <v>79373</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -710,13 +710,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>481028</v>
+        <v>480985</v>
       </c>
       <c r="R2" t="n">
-        <v>6972032</v>
+        <v>6972063</v>
       </c>
       <c r="S2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>11:27</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>11:27</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,14 +782,14 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>133114988</v>
+        <v>133114986</v>
       </c>
       <c r="B3" t="n">
-        <v>79334</v>
+        <v>79373</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -817,13 +817,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>481003</v>
+        <v>481028</v>
       </c>
       <c r="R3" t="n">
-        <v>6971995</v>
+        <v>6972032</v>
       </c>
       <c r="S3" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -852,7 +852,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -862,12 +862,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:59</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -897,11 +892,11 @@
         <v>133114987</v>
       </c>
       <c r="B4" t="n">
-        <v>79334</v>
+        <v>79373</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -998,6 +993,118 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>133114988</v>
+      </c>
+      <c r="B5" t="n">
+        <v>79373</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Västavåga, Jmt</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>481003</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6971995</v>
+      </c>
+      <c r="S5" t="n">
+        <v>6</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Hackås</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>11:59</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>11:59</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Elin Albrechtsson</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Elin Albrechtsson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 20065-2026 artfynd.xlsx
+++ b/artfynd/A 20065-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AZ5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -779,6 +784,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133114985</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -886,6 +896,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133114986</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -993,6 +1008,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133114987</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1105,8 +1125,19 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133114988</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>